--- a/lab2/po_lab2.xlsx
+++ b/lab2/po_lab2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\3course\2sem\PO\PO-labs\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D4693A-BAEA-479D-94AC-C2074D17359E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829C737-C0FC-4F57-B845-47DD690F4D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/lab2/po_lab2.xlsx
+++ b/lab2/po_lab2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\study\3course\2sem\PO\PO-labs\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0829C737-C0FC-4F57-B845-47DD690F4D18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F81004-1358-4B05-A521-DDB89C92D881}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Size</t>
   </si>
@@ -40,6 +40,168 @@
   </si>
   <si>
     <t>Linear</t>
+  </si>
+  <si>
+    <t>Test Results:</t>
+  </si>
+  <si>
+    <t>Matrix Size     Threads Mode    Time (seconds)  XOR Result</t>
+  </si>
+  <si>
+    <t>10000           -       Linear  0.000062        826</t>
+  </si>
+  <si>
+    <t>10000           8       Mutex   0.000763        826</t>
+  </si>
+  <si>
+    <t>10000           16      Mutex   0.000625        826</t>
+  </si>
+  <si>
+    <t>10000           32      Mutex   0.001360        826</t>
+  </si>
+  <si>
+    <t>10000           64      Mutex   0.002714        826</t>
+  </si>
+  <si>
+    <t>10000           128     Mutex   0.005291        826</t>
+  </si>
+  <si>
+    <t>10000           256     Mutex   0.010560        826</t>
+  </si>
+  <si>
+    <t>10000           8       CAS     0.000399        826</t>
+  </si>
+  <si>
+    <t>10000           16      CAS     0.000662        826</t>
+  </si>
+  <si>
+    <t>10000           32      CAS     0.001204        826</t>
+  </si>
+  <si>
+    <t>10000           64      CAS     0.002682        826</t>
+  </si>
+  <si>
+    <t>10000           128     CAS     0.004858        826</t>
+  </si>
+  <si>
+    <t>10000           256     CAS     0.010643        826</t>
+  </si>
+  <si>
+    <t>1000000         -       Linear  0.005860        781</t>
+  </si>
+  <si>
+    <t>1000000         8       Mutex   0.012306        781</t>
+  </si>
+  <si>
+    <t>1000000         16      Mutex   0.010937        781</t>
+  </si>
+  <si>
+    <t>1000000         32      Mutex   0.010299        781</t>
+  </si>
+  <si>
+    <t>1000000         64      Mutex   0.011098        781</t>
+  </si>
+  <si>
+    <t>1000000         128     Mutex   0.012943        781</t>
+  </si>
+  <si>
+    <t>1000000         256     Mutex   0.011305        781</t>
+  </si>
+  <si>
+    <t>1000000         8       CAS     0.000907        781</t>
+  </si>
+  <si>
+    <t>1000000         16      CAS     0.000904        781</t>
+  </si>
+  <si>
+    <t>1000000         32      CAS     0.001278        781</t>
+  </si>
+  <si>
+    <t>1000000         64      CAS     0.002621        781</t>
+  </si>
+  <si>
+    <t>1000000         128     CAS     0.004946        781</t>
+  </si>
+  <si>
+    <t>1000000         256     CAS     0.009590        781</t>
+  </si>
+  <si>
+    <t>100000000               -       Linear  0.588618        324</t>
+  </si>
+  <si>
+    <t>100000000               8       Mutex   1.161741        324</t>
+  </si>
+  <si>
+    <t>100000000               16      Mutex   1.128226        324</t>
+  </si>
+  <si>
+    <t>100000000               32      Mutex   0.959804        324</t>
+  </si>
+  <si>
+    <t>100000000               64      Mutex   0.961426        324</t>
+  </si>
+  <si>
+    <t>100000000               128     Mutex   0.994605        324</t>
+  </si>
+  <si>
+    <t>100000000               256     Mutex   0.960801        324</t>
+  </si>
+  <si>
+    <t>100000000               8       CAS     0.066969        324</t>
+  </si>
+  <si>
+    <t>100000000               16      CAS     0.064933        324</t>
+  </si>
+  <si>
+    <t>100000000               32      CAS     0.055121        324</t>
+  </si>
+  <si>
+    <t>100000000               64      CAS     0.052974        324</t>
+  </si>
+  <si>
+    <t>100000000               128     CAS     0.052699        324</t>
+  </si>
+  <si>
+    <t>100000000               256     CAS     0.054562        324</t>
+  </si>
+  <si>
+    <t>2000000000              -       Linear  11.820394       177</t>
+  </si>
+  <si>
+    <t>2000000000              8       Mutex   23.891283       177</t>
+  </si>
+  <si>
+    <t>2000000000              16      Mutex   23.242272       177</t>
+  </si>
+  <si>
+    <t>2000000000              32      Mutex   19.827012       177</t>
+  </si>
+  <si>
+    <t>2000000000              64      Mutex   18.923028       177</t>
+  </si>
+  <si>
+    <t>2000000000              128     Mutex   18.895269       177</t>
+  </si>
+  <si>
+    <t>2000000000              256     Mutex   19.467100       177</t>
+  </si>
+  <si>
+    <t>2000000000              8       CAS     1.241972        177</t>
+  </si>
+  <si>
+    <t>2000000000              16      CAS     0.958201        177</t>
+  </si>
+  <si>
+    <t>2000000000              32      CAS     0.967178        177</t>
+  </si>
+  <si>
+    <t>2000000000              64      CAS     0.953843        177</t>
+  </si>
+  <si>
+    <t>2000000000              128     CAS     0.928937        177</t>
+  </si>
+  <si>
+    <t>2000000000              256     CAS     0.926709        177</t>
   </si>
 </sst>
 </file>
@@ -308,22 +470,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.5500000000000001E-4</c:v>
+                  <c:v>7.6300000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.8799999999999996E-4</c:v>
+                  <c:v>6.2500000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3829999999999999E-3</c:v>
+                  <c:v>1.3600000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.807E-3</c:v>
+                  <c:v>2.7139999999999998E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0939999999999996E-3</c:v>
+                  <c:v>5.2909999999999997E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.1568999999999999E-2</c:v>
+                  <c:v>1.056E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -380,22 +542,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>3.9800000000000002E-4</c:v>
+                  <c:v>3.9899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7.0299999999999996E-4</c:v>
+                  <c:v>6.6200000000000005E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.2440000000000001E-3</c:v>
+                  <c:v>1.204E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.7880000000000001E-3</c:v>
+                  <c:v>2.6819999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.8279999999999998E-3</c:v>
+                  <c:v>4.8580000000000003E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0585000000000001E-2</c:v>
+                  <c:v>1.0643E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -762,22 +924,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.1709999999999999E-3</c:v>
+                  <c:v>1.2305999999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0089999999999999E-3</c:v>
+                  <c:v>1.0937000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.346E-3</c:v>
+                  <c:v>1.0299000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.532E-3</c:v>
+                  <c:v>1.1098E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.777E-3</c:v>
+                  <c:v>1.2943E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.0156E-2</c:v>
+                  <c:v>1.1305000000000001E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -861,22 +1023,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>9.5799999999999998E-4</c:v>
+                  <c:v>9.0700000000000004E-4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.041E-3</c:v>
+                  <c:v>9.0399999999999996E-4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.31E-3</c:v>
+                  <c:v>1.2780000000000001E-3</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2.64E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.1190000000000003E-3</c:v>
+                  <c:v>4.9459999999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>9.3810000000000004E-3</c:v>
+                  <c:v>9.5899999999999996E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1243,22 +1405,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.3966999999999996E-2</c:v>
+                  <c:v>1.1617409999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5.8313999999999998E-2</c:v>
+                  <c:v>1.128226</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.2195999999999999E-2</c:v>
+                  <c:v>0.95980399999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.4623999999999999E-2</c:v>
+                  <c:v>0.961426</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.0994999999999999E-2</c:v>
+                  <c:v>0.99460499999999996</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.2724E-2</c:v>
+                  <c:v>0.96080100000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1342,22 +1504,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>6.1608000000000003E-2</c:v>
+                  <c:v>6.6969000000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.2660999999999994E-2</c:v>
+                  <c:v>6.4933000000000005E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.3881999999999999E-2</c:v>
+                  <c:v>5.5121000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5.7091999999999997E-2</c:v>
+                  <c:v>5.2974E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.5183000000000003E-2</c:v>
+                  <c:v>5.2699000000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.5036000000000002E-2</c:v>
+                  <c:v>5.4561999999999999E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1720,22 +1882,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.247409</c:v>
+                  <c:v>23.891283000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.037957</c:v>
+                  <c:v>23.242272</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.96950400000000003</c:v>
+                  <c:v>19.827012</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.96986499999999998</c:v>
+                  <c:v>18.923027999999999</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.94126900000000002</c:v>
+                  <c:v>18.895268999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.984128</c:v>
+                  <c:v>19.467099999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1819,22 +1981,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>1.2137</c:v>
+                  <c:v>1.2419720000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.008956</c:v>
+                  <c:v>0.95820099999999997</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.031334</c:v>
+                  <c:v>0.96717799999999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.98956100000000002</c:v>
+                  <c:v>0.953843</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.025021</c:v>
+                  <c:v>0.92893700000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.023752</c:v>
+                  <c:v>0.926709</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4633,14 +4795,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E62"/>
+  <dimension ref="A2:Q70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
     <col min="3" max="4" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
@@ -4649,7 +4811,7 @@
       </c>
       <c r="D2" s="7"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -4659,103 +4821,158 @@
       <c r="D3" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Q3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4">
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>9.5500000000000001E-4</v>
+        <v>7.6300000000000001E-4</v>
       </c>
       <c r="D4" s="1">
-        <v>3.9800000000000002E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3.9899999999999999E-4</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>16</v>
       </c>
       <c r="C5" s="1">
-        <v>7.8799999999999996E-4</v>
+        <v>6.2500000000000001E-4</v>
       </c>
       <c r="D5" s="1">
-        <v>7.0299999999999996E-4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>6.6200000000000005E-4</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>32</v>
       </c>
       <c r="C6" s="1">
-        <v>1.3829999999999999E-3</v>
+        <v>1.3600000000000001E-3</v>
       </c>
       <c r="D6" s="1">
-        <v>1.2440000000000001E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.204E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>64</v>
       </c>
       <c r="C7" s="1">
-        <v>2.807E-3</v>
+        <v>2.7139999999999998E-3</v>
       </c>
       <c r="D7" s="1">
-        <v>2.7880000000000001E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>2.6819999999999999E-3</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>128</v>
       </c>
       <c r="C8" s="1">
-        <v>5.0939999999999996E-3</v>
+        <v>5.2909999999999997E-3</v>
       </c>
       <c r="D8" s="1">
-        <v>5.8279999999999998E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>4.8580000000000003E-3</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>256</v>
       </c>
       <c r="C9" s="1">
-        <v>1.1568999999999999E-2</v>
+        <v>1.056E-2</v>
       </c>
       <c r="D9" s="5">
-        <v>1.0585000000000001E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1.0643E-2</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Q10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C11" s="3">
-        <v>5.8E-5</v>
+        <v>6.2000000000000003E-5</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Q11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="Q12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="D13" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="E17" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="Q17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="4" t="s">
         <v>0</v>
       </c>
@@ -4764,7 +4981,7 @@
       </c>
       <c r="D20" s="7"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
         <v>1</v>
       </c>
@@ -4775,87 +4992,133 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="4">
         <v>8</v>
       </c>
       <c r="C22" s="1">
-        <v>1.1709999999999999E-3</v>
+        <v>1.2305999999999999E-2</v>
       </c>
       <c r="D22" s="1">
-        <v>9.5799999999999998E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9.0700000000000004E-4</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="4">
         <v>16</v>
       </c>
       <c r="C23" s="1">
-        <v>1.0089999999999999E-3</v>
+        <v>1.0937000000000001E-2</v>
       </c>
       <c r="D23" s="1">
-        <v>1.041E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9.0399999999999996E-4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="4">
         <v>32</v>
       </c>
       <c r="C24" s="1">
-        <v>1.346E-3</v>
+        <v>1.0299000000000001E-2</v>
       </c>
       <c r="D24" s="1">
-        <v>1.31E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+        <v>1.2780000000000001E-3</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="4">
         <v>64</v>
       </c>
       <c r="C25" s="1">
-        <v>2.532E-3</v>
+        <v>1.1098E-2</v>
       </c>
       <c r="D25" s="1">
         <v>2.64E-3</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="Q25" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="4">
         <v>128</v>
       </c>
       <c r="C26" s="1">
-        <v>4.777E-3</v>
+        <v>1.2943E-2</v>
       </c>
       <c r="D26" s="1">
-        <v>5.1190000000000003E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+        <v>4.9459999999999999E-3</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="4">
         <v>256</v>
       </c>
       <c r="C27" s="1">
-        <v>1.0156E-2</v>
+        <v>1.1305000000000001E-2</v>
       </c>
       <c r="D27" s="5">
-        <v>9.3810000000000004E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+        <v>9.5899999999999996E-3</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="Q28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B29" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="3">
-        <v>5.9849999999999999E-3</v>
+        <v>5.8599999999999998E-3</v>
       </c>
       <c r="D29" s="3"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q29" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q31" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q34" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B36" s="4" t="s">
         <v>0</v>
       </c>
@@ -4863,8 +5126,11 @@
         <v>100000000</v>
       </c>
       <c r="D36" s="7"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q36" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
         <v>1</v>
       </c>
@@ -4875,87 +5141,135 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B38" s="4">
         <v>8</v>
       </c>
       <c r="C38" s="1">
-        <v>6.3966999999999996E-2</v>
+        <v>1.1617409999999999</v>
       </c>
       <c r="D38" s="1">
-        <v>6.1608000000000003E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+        <v>6.6969000000000001E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B39" s="4">
         <v>16</v>
       </c>
       <c r="C39" s="1">
-        <v>5.8313999999999998E-2</v>
+        <v>1.128226</v>
       </c>
       <c r="D39" s="1">
-        <v>6.2660999999999994E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+        <v>6.4933000000000005E-2</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B40" s="4">
         <v>32</v>
       </c>
       <c r="C40" s="1">
-        <v>5.2195999999999999E-2</v>
+        <v>0.95980399999999999</v>
       </c>
       <c r="D40" s="1">
-        <v>5.3881999999999999E-2</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5.5121000000000003E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B41" s="4">
         <v>64</v>
       </c>
       <c r="C41" s="1">
-        <v>5.4623999999999999E-2</v>
+        <v>0.961426</v>
       </c>
       <c r="D41" s="1">
-        <v>5.7091999999999997E-2</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5.2974E-2</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B42" s="4">
         <v>128</v>
       </c>
       <c r="C42" s="1">
-        <v>5.0994999999999999E-2</v>
+        <v>0.99460499999999996</v>
       </c>
       <c r="D42" s="1">
-        <v>5.5183000000000003E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5.2699000000000003E-2</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B43" s="4">
         <v>256</v>
       </c>
       <c r="C43" s="1">
-        <v>5.2724E-2</v>
+        <v>0.96080100000000002</v>
       </c>
       <c r="D43" s="5">
-        <v>5.5036000000000002E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+        <v>5.4561999999999999E-2</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q44" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B45" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C45" s="3">
-        <v>0.59597900000000004</v>
+        <v>0.58861799999999997</v>
       </c>
       <c r="D45" s="3"/>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q45" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q46" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q49" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q51" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q52" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
         <v>0</v>
       </c>
@@ -4963,8 +5277,11 @@
         <v>2000000000</v>
       </c>
       <c r="D53" s="7"/>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q53" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
         <v>1</v>
       </c>
@@ -4975,85 +5292,138 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="4">
         <v>8</v>
       </c>
       <c r="C55" s="1">
-        <v>1.247409</v>
+        <v>23.891283000000001</v>
       </c>
       <c r="D55" s="1">
-        <v>1.2137</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+        <v>1.2419720000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B56" s="4">
         <v>16</v>
       </c>
       <c r="C56" s="1">
-        <v>1.037957</v>
+        <v>23.242272</v>
       </c>
       <c r="D56" s="1">
-        <v>1.008956</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+        <v>0.95820099999999997</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B57" s="4">
         <v>32</v>
       </c>
       <c r="C57" s="1">
-        <v>0.96950400000000003</v>
+        <v>19.827012</v>
       </c>
       <c r="D57" s="1">
-        <v>1.031334</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+        <v>0.96717799999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B58" s="4">
         <v>64</v>
       </c>
       <c r="C58" s="1">
-        <v>0.96986499999999998</v>
+        <v>18.923027999999999</v>
       </c>
       <c r="D58" s="1">
-        <v>0.98956100000000002</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+        <v>0.953843</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B59" s="4">
         <v>128</v>
       </c>
       <c r="C59" s="1">
-        <v>0.94126900000000002</v>
+        <v>18.895268999999999</v>
       </c>
       <c r="D59" s="1">
-        <v>1.025021</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+        <v>0.92893700000000001</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B60" s="4">
         <v>256</v>
       </c>
       <c r="C60" s="1">
-        <v>0.984128</v>
+        <v>19.467099999999999</v>
       </c>
       <c r="D60" s="5">
-        <v>1.023752</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+        <v>0.926709</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="Q61" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B62" s="3" t="s">
         <v>4</v>
       </c>
       <c r="C62" s="3">
-        <v>12.182086999999999</v>
+        <v>11.820394</v>
       </c>
       <c r="D62" s="3"/>
+      <c r="Q62" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q65" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="66" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q66" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="67" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q67" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="68" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q68" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q69" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="70" spans="17:17" x14ac:dyDescent="0.25">
+      <c r="Q70" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
